--- a/files/dbdirk/Boligberegning_2025.xlsx
+++ b/files/dbdirk/Boligberegning_2025.xlsx
@@ -53,34 +53,11 @@
             Inkluderer flytning, eventuel renovering og andre engangsomkostninger.</t>
       </text>
     </comment>
-    <comment ref="A12" authorId="0">
-      <text>
-        <t xml:space="preserve">Beregning af minimumsbeløb:
-            1. Omkostninger:
-              Skøde/Tinglysning: 39.620 kr.
-              Advokat: 5.000 kr.
-              Ejerskifteforsikring: 9.583 kr.
-              Flytteomkostninger: 20.000 kr.
-              Total omkostninger: 74.203 kr.
-            2. Minimum efter omkostninger:
-              5% af kontantværdi (6.295.000 kr. × 5%)
-              = 314.750 kr.
-            3. Total minimumsbeløb:
-              Omkostninger + Minimum efter omkostninger
-              74.203 kr. + 314.750 kr.
-              = 388.953 kr.
-            Formel: Minimum = (Kontantpris × 5%) + Omkostninger
-                Nuværende efter omkostninger: 925.797 kr. ✓</t>
-      </text>
-    </comment>
     <comment ref="A13" authorId="0">
       <text>
         <t xml:space="preserve">Hovedstolen er den realkreditbeløb der skal til for at finansiere købet (op til 80% af kontantværdien). Ved høj udbetaling sænkes hovedstolen, så den matcher behovet.
             Andel af pris: 80,0%
-            Hovedstol: 5.036.000 kr.
-            Provenu: 4.995.784 kr.
-            Låneomkostninger: 40.216 kr.
-            Provenuet er lavere end hovedstolen pga. tinglysning af pant, etablering m.m.</t>
+            Hovedstol: 5.036.000 kr.</t>
       </text>
     </comment>
   </commentList>
@@ -102,10 +79,7 @@
       <text>
         <t xml:space="preserve">Hovedstolen er den realkreditbeløb der skal til for at finansiere købet (op til 80% af kontantværdien). Ved høj udbetaling sænkes hovedstolen, så den matcher behovet.
             Andel af pris: 80,0%
-            Hovedstol: 5.036.000 kr.
-            Provenu: 4.995.784 kr.
-            Låneomkostninger: 40.216 kr.
-            Provenuet er lavere end hovedstolen pga. tinglysning af pant, etablering m.m.</t>
+            Hovedstol: 5.036.000 kr.</t>
       </text>
     </comment>
     <comment ref="A3" authorId="0">
@@ -142,10 +116,7 @@
       <text>
         <t xml:space="preserve">Hovedstolen er den realkreditbeløb der skal til for at finansiere købet (op til 80% af kontantværdien). Ved høj udbetaling sænkes hovedstolen, så den matcher behovet.
             Andel af pris: 80,0%
-            Hovedstol: 5.036.000 kr.
-            Provenu: 4.995.784 kr.
-            Låneomkostninger: 40.216 kr.
-            Provenuet er lavere end hovedstolen pga. tinglysning af pant, etablering m.m.</t>
+            Hovedstol: 5.036.000 kr.</t>
       </text>
     </comment>
     <comment ref="A3" authorId="0">
@@ -182,10 +153,7 @@
       <text>
         <t xml:space="preserve">Hovedstolen er den realkreditbeløb der skal til for at finansiere købet (op til 80% af kontantværdien). Ved høj udbetaling sænkes hovedstolen, så den matcher behovet.
             Andel af pris: 80,0%
-            Hovedstol: 5.036.000 kr.
-            Provenu: 4.995.784 kr.
-            Låneomkostninger: 40.216 kr.
-            Provenuet er lavere end hovedstolen pga. tinglysning af pant, etablering m.m.</t>
+            Hovedstol: 5.036.000 kr.</t>
       </text>
     </comment>
     <comment ref="A3" authorId="0">
@@ -222,10 +190,7 @@
       <text>
         <t xml:space="preserve">Hovedstolen er den realkreditbeløb der skal til for at finansiere købet (op til 80% af kontantværdien). Ved høj udbetaling sænkes hovedstolen, så den matcher behovet.
             Andel af pris: 80,0%
-            Hovedstol: 5.036.000 kr.
-            Provenu: 4.995.784 kr.
-            Låneomkostninger: 40.216 kr.
-            Provenuet er lavere end hovedstolen pga. tinglysning af pant, etablering m.m.</t>
+            Hovedstol: 5.036.000 kr.</t>
       </text>
     </comment>
     <comment ref="A3" authorId="0">
@@ -689,7 +654,7 @@
         <v>Advokat</v>
       </c>
       <c r="B6" s="1">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="7">
@@ -753,7 +718,7 @@
         <v>Banklån (Hovedstol)</v>
       </c>
       <c r="B14" s="1">
-        <v>382759</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="15">
@@ -769,7 +734,7 @@
         <v>Dato</v>
       </c>
       <c r="B16" t="str">
-        <v>23.3.2026</v>
+        <v>25.3.2026</v>
       </c>
     </row>
   </sheetData>
